--- a/reconciliation-contenu-teleexpertise/ig/StructureDefinition-cfl-ServiceRequest-requerant.xlsx
+++ b/reconciliation-contenu-teleexpertise/ig/StructureDefinition-cfl-ServiceRequest-requerant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:58:57+00:00</t>
+    <t>2026-07-24T15:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -912,7 +912,7 @@
     <t>ServiceRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/teleexpertise-confluence/StructureDefinition/fr-core-patient-cfl|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/teleexpertise-confluence/StructureDefinition/cfl-patient|0.1.0)
 </t>
   </si>
   <si>
